--- a/AIVIA_Design/L1_KG1_Technical_Layer_Registry.xlsx
+++ b/AIVIA_Design/L1_KG1_Technical_Layer_Registry.xlsx
@@ -459,7 +459,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>DRAFT v0.1 — the technical layer's METAMODEL REGISTRY: the executable twin of 'Content Descriptions Level 1' in the AIVIA Design Document. The DOC is the design authority; this registry is what code and tests will consume. Protocol rule: any doc change to L1 updates this registry in the same breath.</t>
+          <t>DRAFT v0.1 — the technical layer's METAMODEL REGISTRY: the executable twin of 'Content Descriptions Level 1' in the AISQL Design Document. The DOC is the design authority; this registry is what code and tests will consume. Protocol rule: any doc change to L1 updates this registry in the same breath.</t>
         </is>
       </c>
     </row>
